--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>odds_home</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>odds_draw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>odds_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>dnnqk0iD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,88 +448,660 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>YH892O2B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>8jyraADG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>9.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dnnqk0iD</t>
+          <t>4xHh663n</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>6RvR2hEi</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0lGMiS5j</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>hKOA02XN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>O2Fteteo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Sf88FVcc</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>42SH31wI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>02s0k9od</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>5.00</t>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2.40</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>EirZ0Wr4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -458,78 +458,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>dnnqk0iD</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>QT6wuRFc</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>5.00</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,71 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>odds_home</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>odds_draw</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>odds_away</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>EirZ0Wr4</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>t4ZkclrT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>odds_home</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>odds_draw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>odds_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,78 +448,78 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>12.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,7 +529,139 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>3.60</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.40</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,95 +448,95 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0IkylEqd</t>
+          <t>hCxNBHy3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -558,110 +558,22 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CEhO9e6F</t>
+          <t>KvdW7ZzS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>CxyB0iT1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>CSXdOfL8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>ptW4MYkL</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
           <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>4QCyHCDr</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3.40</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,34 +448,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>4.33</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,85 +485,85 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>zVpmZBZQ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>SSPRRTR0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hCxNBHy3</t>
+          <t>p4dhrkCs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KvdW7ZzS</t>
+          <t>Y54hDUC7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,7 +573,139 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>3.10</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Eql9v7B6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.90</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,78 +448,78 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zVpmZBZQ</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SSPRRTR0</t>
+          <t>dtLQNtsB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,46 +529,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>p4dhrkCs</t>
+          <t>Ofy73Ced</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Y54hDUC7</t>
+          <t>CGH1PgIF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -580,132 +580,44 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v3ivyY4E</t>
+          <t>21OYHBAk</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>W0WITkcl</t>
+          <t>v3JgRFm3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>YPSZP7dD</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>EL5MmBlK</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tWk1tTtf</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Eql9v7B6</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2.90</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,176 +448,220 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>dtLQNtsB</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Ofy73Ced</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CGH1PgIF</t>
+          <t>v5l07LdU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>21OYHBAk</t>
+          <t>fHO9ROsn</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>v3JgRFm3</t>
+          <t>jqIIP2Cb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>3.20</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>3.70</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.00</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,132 +536,4092 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>v5l07LdU</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>fHO9ROsn</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jqIIP2Cb</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GUXb5YQq</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>UilLdutJ</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2uc40Ntf</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>M7MVoOR0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dbt7KrYP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AsIP75lK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6D3e2qCs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>EirZ0Wr4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>t4ZkclrT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>YH892O2B</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>8jyraADG</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>6RvR2hEi</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>0lGMiS5j</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>hKOA02XN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>O2Fteteo</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Sf88FVcc</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>0OKRs71U</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>4W5t03Zl</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>rN4paNle</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>6Le197C2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>jPP565dL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>pnP95PBR</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>CYQ17osF</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>pCf58RR8</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>hI7JpOZ1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Cd9lbs41</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>M7Gy1qKr</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>rmlyYpjd</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Q7Nvh6sS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>nHOzgnSL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>beWNelr3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>4hZVgSCF</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>vF3Fo4Ke</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>IaF6mQkq</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>djEAnp5k</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>hIVRf8c9</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>K4XJdUSd</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>UFIypiqi</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>jk9duTcM</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>GCUgL76j</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>4YAlskT9</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>QsCprVD3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>4dkXYQzj</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>CbAht9rG</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>YDb1vmDS</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>AZkTZ6Lq</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>rJMuqBbc</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>MBCLwGMH</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>jDeAtIxa</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>8l65sbNh</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>0O2cqKht</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>bFGVm0pP</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>xMVkMmip</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>fsjku8tP</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>lbEDuxh5</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>Uc71rv8n</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>rLDHvd7B</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>dQhciEZJ</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>tvnotlRI</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>8QmwrAd6</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>SEWuqjs0</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>nHnssUBC</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>zHi1jYlQ</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>f1YXpCCm</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>tbUTohcs</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>lOXypWRg</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>8AaFSUdJ</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>f1nTGXc7</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5.09</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>rNSNxFKQ</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>279fXhrl</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>pWEkYYSs</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>tb8bWCcf</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>neB6UjS6</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>zL72VWC0</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>UJ0BTAsD</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>zcPFvyjE</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>YioXFiDD</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>l0TJwe5K</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>K6Cj3ET7</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>C0axRHLE</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>UyfsQyyL</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>MZYLIgTf</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>vBqHJZDl</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>Y90YRc68</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>0QXPHDr1</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>Q7uDKFbr</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>8ShoPejR</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>Q7Js5zae</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>pjacQpV3</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>CpeE3NNj</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>8W8n4fE1</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>tIh6OOaG</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>jTagRQFc</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>Cx1kS60i</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>IsGZ6dUr</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>bg31P4pA</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>nHKw6Gqk</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>CMCRCR04</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>KnGZA5VG</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>hM5FFTGo</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>GE9r9q0T</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>vJHXjpvo</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>j7OIEmWi</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>tdHVBoGA</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>YVDND7ob</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>YgdA438p</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>2B5vAPpN</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>C2pt1U1h</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>nLxgbSoB</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>xAV5eQVT</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>jgqp0lHb</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>4xox2Ann</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>trxccn1H</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>YHYla8W4</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>KYz1d6GN</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>QonY2jXu</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>42SH31wI</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>02s0k9od</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>dnnqk0iD</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>v5l07LdU</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>fHO9ROsn</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>jqIIP2Cb</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
           <t>WIX2NXnS</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>2.40</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>3.20</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>dtLQNtsB</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>Ofy73Ced</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>CGH1PgIF</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>21OYHBAk</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>v3JgRFm3</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>zVpmZBZQ</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>SSPRRTR0</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>p4dhrkCs</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>Y54hDUC7</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>Eql9v7B6</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>hCxNBHy3</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>KvdW7ZzS</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2.40</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,176 +448,264 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>v1I9TP43</t>
+          <t>rgFQPs4S</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>n7VN5MCd</t>
+          <t>WIJkQBF8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OGCsGku2</t>
+          <t>Esk5Iad2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jN4TwgX8</t>
+          <t>6cNF7rrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.75</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OUiGUlfe</t>
+          <t>zFWqD4KM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CjYAjWGE</t>
+          <t>4WHcOkpL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>b7WIlAoR</t>
+          <t>zTBIR3ZF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>S2b7WAPr</t>
+          <t>SQjcKLRk</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>j5BcsSw1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WWCyxX1L</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WfeOSSO7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>IiDkql9l</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>2.90</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>3.40</t>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3.20</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,139 +448,139 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>v1I9TP43</t>
+          <t>xIieTySH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>n7VN5MCd</t>
+          <t>WvDUsysB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OGCsGku2</t>
+          <t>pOEMqcCb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jN4TwgX8</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OUiGUlfe</t>
+          <t>O8QDoJsn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CjYAjWGE</t>
+          <t>Yqo4RFdU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>b7WIlAoR</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -595,29 +595,227 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>S2b7WAPr</t>
+          <t>44gmVcc5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>zTBIR3ZF</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>SQjcKLRk</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>11.00</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,78 +448,78 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xIieTySH</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WvDUsysB</t>
+          <t>h8xCR9dC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>11.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pOEMqcCb</t>
+          <t>OE5MGhrf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>A50vXJSh</t>
+          <t>baMp22np</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,293 +529,117 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>O8QDoJsn</t>
+          <t>xCj1xWPj</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Yqo4RFdU</t>
+          <t>h2uVDr1f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>S66wtFBN</t>
+          <t>SG7bDmCr</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>44gmVcc5</t>
+          <t>WjBv9U0S</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2ucWYubt</t>
+          <t>O2Xm0vko</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>rgFQPs4S</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>WIJkQBF8</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Esk5Iad2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>6cNF7rrp</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>zFWqD4KM</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
           <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4WHcOkpL</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>zTBIR3ZF</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>SQjcKLRk</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>11.00</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,166 +448,166 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OAeKROjD</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h8xCR9dC</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OE5MGhrf</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.45</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>baMp22np</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>9.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>xCj1xWPj</t>
+          <t>jwmmlzio</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>3.90</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>h2uVDr1f</t>
+          <t>vaTsAHD4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SG7bDmCr</t>
+          <t>4USV4sgM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WjBv9U0S</t>
+          <t>8vLb6ZCT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,29 +617,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>O2Xm0vko</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4.75</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,176 +448,198 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>9.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jwmmlzio</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vaTsAHD4</t>
+          <t>nPWk8erH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4USV4sgM</t>
+          <t>ID6U0Dzi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8vLb6ZCT</t>
+          <t>zkyF8Pgc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>82ZM63O9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.80</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,176 +448,5676 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>9.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jwmmlzio</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vaTsAHD4</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4USV4sgM</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>zTBIR3ZF</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>SQjcKLRk</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>v1I9TP43</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>n7VN5MCd</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>UilLdutJ</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>2uc40Ntf</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>M7MVoOR0</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>dbt7KrYP</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>AsIP75lK</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>6D3e2qCs</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>EirZ0Wr4</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>t4ZkclrT</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>YH892O2B</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>8jyraADG</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>6RvR2hEi</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>0lGMiS5j</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>hKOA02XN</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>O2Fteteo</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>Sf88FVcc</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>0OKRs71U</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>4W5t03Zl</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>rN4paNle</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>6Le197C2</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>jPP565dL</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>pnP95PBR</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>CYQ17osF</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>pCf58RR8</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>hI7JpOZ1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>Cd9lbs41</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>M7Gy1qKr</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>rmlyYpjd</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>Q7Nvh6sS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>nHOzgnSL</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>beWNelr3</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>4hZVgSCF</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>vF3Fo4Ke</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>IaF6mQkq</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>djEAnp5k</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>hIVRf8c9</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>K4XJdUSd</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>UFIypiqi</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>jk9duTcM</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>GCUgL76j</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>4YAlskT9</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>QsCprVD3</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>4dkXYQzj</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>CbAht9rG</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>YDb1vmDS</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>AZkTZ6Lq</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>rJMuqBbc</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>MBCLwGMH</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>jDeAtIxa</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>8l65sbNh</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>0O2cqKht</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>bFGVm0pP</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>xMVkMmip</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>fsjku8tP</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>lbEDuxh5</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>Uc71rv8n</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>rLDHvd7B</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>dQhciEZJ</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>tvnotlRI</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>8QmwrAd6</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>SEWuqjs0</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>nHnssUBC</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>zHi1jYlQ</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>f1YXpCCm</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>tbUTohcs</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>lOXypWRg</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>8AaFSUdJ</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>f1nTGXc7</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5.09</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>rNSNxFKQ</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>279fXhrl</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>pWEkYYSs</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>tb8bWCcf</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>neB6UjS6</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>zL72VWC0</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>UJ0BTAsD</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>zcPFvyjE</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>YioXFiDD</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>l0TJwe5K</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>K6Cj3ET7</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>C0axRHLE</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>UyfsQyyL</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>MZYLIgTf</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>vBqHJZDl</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>Y90YRc68</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>0QXPHDr1</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>Q7uDKFbr</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>8ShoPejR</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>Q7Js5zae</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>pjacQpV3</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>CpeE3NNj</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>8W8n4fE1</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>tIh6OOaG</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>jTagRQFc</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>Cx1kS60i</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>IsGZ6dUr</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>bg31P4pA</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>nHKw6Gqk</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>CMCRCR04</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>KnGZA5VG</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>hM5FFTGo</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>GE9r9q0T</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>vJHXjpvo</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>j7OIEmWi</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>tdHVBoGA</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>YVDND7ob</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>YgdA438p</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>2B5vAPpN</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>C2pt1U1h</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>nLxgbSoB</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>xAV5eQVT</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>jgqp0lHb</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>4xox2Ann</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>trxccn1H</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>YHYla8W4</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>KYz1d6GN</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>QonY2jXu</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>h8xCR9dC</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>OE5MGhrf</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>baMp22np</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>xCj1xWPj</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>h2uVDr1f</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>SG7bDmCr</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>WjBv9U0S</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>O2Xm0vko</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>42SH31wI</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>02s0k9od</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>dnnqk0iD</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>rXZYBwqh</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>KfY0aLGq</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>nPWk8erH</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>ID6U0Dzi</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>zkyF8Pgc</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>82ZM63O9</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>jwmmlzio</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>vaTsAHD4</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>4USV4sgM</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
           <t>8vLb6ZCT</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>2.38</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C199" t="inlineStr">
         <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>drYOcmOs</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>48yXeRhf</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>YL6GgdTN</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>0zVuf5N6</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>CAdh390K</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>YmTmhqhJ</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>dGBia0an</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>4tFacvUb</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>Qe38eIbB</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>nX46u68D</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>j5BcsSw1</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>WWCyxX1L</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>WfeOSSO7</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>IiDkql9l</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>OGCsGku2</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>jN4TwgX8</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>OUiGUlfe</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>CjYAjWGE</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>b7WIlAoR</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>S2b7WAPr</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>v5l07LdU</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>fHO9ROsn</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>jqIIP2Cb</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>dtLQNtsB</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>Ofy73Ced</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>CGH1PgIF</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>21OYHBAk</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>v3JgRFm3</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>zVpmZBZQ</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>SSPRRTR0</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>p4dhrkCs</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>Y54hDUC7</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>Eql9v7B6</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>hCxNBHy3</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>KvdW7ZzS</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2.40</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,225 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>odds_home</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>odds_draw</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>odds_away</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>EB8yv2aJ</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>WUqjkmPH</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>8SWavWAa</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>z3jsi9f5</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>xd6CHKxS</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>8xjWXuN8</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8zBCDByf</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>tl9KBk66</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>EyI3FX6s</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,225 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>odds_home</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>odds_draw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>odds_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>SznSCTAl</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4MfFXWSP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Imw2OSkC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>UR6KtA5t</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dvbywS45</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>441qy6ZH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xG2T9TzJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,198 +448,22 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SznSCTAl</t>
+          <t>McP0d8Q7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Cl5M5C3L</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>EXLhbUee</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>4MfFXWSP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>3.40</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Imw2OSkC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>UR6KtA5t</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>dvbywS45</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>441qy6ZH</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>xG2T9TzJ</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4.50</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,49 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>odds_home</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>odds_draw</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>odds_away</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>McP0d8Q7</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>odds_home</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>odds_draw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>odds_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>